--- a/ideas_scored.xlsx
+++ b/ideas_scored.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ51"/>
+  <dimension ref="A1:AW51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,105 +541,135 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>pairwise_wins</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>pairwise_rank</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>spearman_rank_correlation</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>llama_status</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>mistral_status</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>mistral_feedback</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>mistral_novelty</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>mistral_feasibility</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>mistral_impact</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>mistral_presentation</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>mistral_overall</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>qwen_status</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>qwen_feedback</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>qwen_novelty</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>qwen_feasibility</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>qwen_impact</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>qwen_presentation</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>qwen_overall</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>combined_feedback</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>score_spread</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>human_review_required</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>mistral_rank</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>qwen_rank</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>llama_accuracy</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>mistral_accuracy</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>qwen_accuracy</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>combined_accuracy</t>
         </is>
@@ -694,22 +724,23 @@
         <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>38</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>3.22</v>
+        <v>2.7</v>
       </c>
       <c r="T2" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -717,70 +748,81 @@
       <c r="V2" t="n">
         <v>0</v>
       </c>
-      <c r="W2" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>3</v>
-      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>3</v>
       </c>
       <c r="AE2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>3.05</v>
-      </c>
+        <v>3.35</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM2" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AN2" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>96</v>
-      </c>
+        <v>2.55</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="n">
-        <v>72</v>
+        <v>0.8</v>
       </c>
       <c r="AQ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW2" t="n">
         <v>84</v>
       </c>
     </row>
@@ -833,22 +875,23 @@
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>39</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="T3" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -856,70 +899,81 @@
       <c r="V3" t="n">
         <v>0</v>
       </c>
-      <c r="W3" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>3</v>
-      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF3" t="n">
         <v>3</v>
       </c>
       <c r="AG3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN3" t="n">
         <v>2.7</v>
       </c>
-      <c r="AJ3" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>96</v>
-      </c>
+      <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="n">
-        <v>72</v>
+        <v>0.65</v>
       </c>
       <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW3" t="n">
         <v>84</v>
       </c>
     </row>
@@ -969,110 +1023,108 @@
         <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>3.65</v>
+        <v>2.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>8</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>Based on the project scores, I've identified the weakest area as "presentation" with a score of 3.0/4. Here are three specific, actionable suggestions to improve it:
-1. **Create an engaging UI/UX**: Invest time in designing an intuitive and visually appealing interface that makes users feel comfortable interacting with the chatbot. Consider using a clean design, simple navigation, and clear typography to ensure that users can easily understand the study plan and track their progress.
-2. **Develop a compelling onboarding experience**: Craft a warm welcome message that sets the tone for the user's journey with StudyBuddy. This could include a brief introduction to the chatbot's capabilities, an explanation of how it works, and some encouraging words to motivate users to start using the platform. Make sure</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>3.52</v>
+        <v>2.85</v>
       </c>
       <c r="T4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Based on the project scores, I've identified the weakest area as "presentation" with a score of 3.0/4. Here are three specific, actionable suggestions to improve it:
-1. **Create an engaging UI/UX**: Invest time in designing an intuitive and visually appealing interface that makes users feel comfortable interacting with the chatbot. Consider using a clean design, simple navigation, and clear typography to ensure that users can easily understand the study plan and track their progress.
-2. **Develop a compelling onboarding experience**: Craft a warm welcome message that sets the tone for the user's journey with StudyBuddy. This could include a brief introduction to the chatbot's capabilities, an explanation of how it works, and some encouraging words to motivate users to start using the platform. Make sure</t>
-        </is>
-      </c>
+        <v>3.4</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN4" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>96</v>
-      </c>
+        <v>2.85</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>72</v>
+        <v>0.7</v>
       </c>
       <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW4" t="n">
         <v>84</v>
       </c>
     </row>
@@ -1119,36 +1171,36 @@
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
         <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Based on the scores provided, it seems that the project has a strong novelty and impact, but may need some improvement in terms of feasibility and presentation. Here are three specific, actionable suggestions to address these weaknesses:
-1. **Feasibility: Refine the multispectral imaging system**
-The current score for feasibility is 3.0/4, which suggests that there may be technical challenges or limitations with the proposed solution. To improve this, I would suggest conducting a thorough review of existing multispectral imaging technologies and identifying potential partners or suppliers who can provide high-quality sensors at an affordable price. Additionally, consider exploring alternative approaches, such as using satellite imagery or machine learning algorithms to process existing camera data, to reduce costs and increase feasibility.
-2. **Presentation: Develop a clear and concise business model</t>
+          <t>Based on the scores, the weakest area is feasibility, with a score of 2.0/4. Here are three specific, actionable suggestions to improve it:
+1. **Conduct a detailed cost-benefit analysis**: Estimate the costs of purchasing and maintaining drones, software, and hardware, as well as the potential revenue generated by the alerts and treatment recommendations.
+2. **Develop a prototype with a low-cost drone**: Use a low-cost drone like a Parrot Anafi or a DJI Spark to test the feasibility of the system and gather data on the effectiveness of the multispectral imaging.
+3. **Research and explore existing drone-based agricultural solutions**: Investigate existing projects and companies that use drones for agricultural monitoring, and analyze their approaches to identify potential partnerships or collaborations that can improve the feasibility</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>3.43</v>
+        <v>3.2</v>
       </c>
       <c r="T5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
         <v>1</v>
@@ -1156,78 +1208,88 @@
       <c r="V5" t="n">
         <v>1</v>
       </c>
-      <c r="W5" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>3</v>
-      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF5" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Based on the scores provided, it seems that the project has a strong novelty and impact, but may need some improvement in terms of feasibility and presentation. Here are three specific, actionable suggestions to address these weaknesses:
-1. **Feasibility: Refine the multispectral imaging system**
-The current score for feasibility is 3.0/4, which suggests that there may be technical challenges or limitations with the proposed solution. To improve this, I would suggest conducting a thorough review of existing multispectral imaging technologies and identifying potential partners or suppliers who can provide high-quality sensors at an affordable price. Additionally, consider exploring alternative approaches, such as using satellite imagery or machine learning algorithms to process existing camera data, to reduce costs and increase feasibility.
-2. **Presentation: Develop a clear and concise business model</t>
-        </is>
-      </c>
+        <v>3.58</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>0.65</v>
+        <v>3</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM5" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AN5" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>96</v>
+        <v>3.2</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Based on the scores, the weakest area is feasibility, with a score of 2.0/4. Here are three specific, actionable suggestions to improve it:
+1. **Conduct a detailed cost-benefit analysis**: Estimate the costs of purchasing and maintaining drones, software, and hardware, as well as the potential revenue generated by the alerts and treatment recommendations.
+2. **Develop a prototype with a low-cost drone**: Use a low-cost drone like a Parrot Anafi or a DJI Spark to test the feasibility of the system and gather data on the effectiveness of the multispectral imaging.
+3. **Research and explore existing drone-based agricultural solutions**: Investigate existing projects and companies that use drones for agricultural monitoring, and analyze their approaches to identify potential partnerships or collaborations that can improve the feasibility</t>
+        </is>
       </c>
       <c r="AP5" t="n">
-        <v>72</v>
+        <v>0.53</v>
       </c>
       <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW5" t="n">
         <v>84</v>
       </c>
     </row>
@@ -1274,36 +1336,33 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N6" t="n">
         <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Based on the scores provided, it seems that the project has a strong novelty and impact, but may require some improvement in feasibility and presentation. Here are three specific, actionable suggestions to address these weaknesses:
-1. **Feasibility: Improve Hand Gesture Recognition Accuracy**
-To increase the feasibility of the project, focus on refining the hand gesture recognition algorithm to achieve higher accuracy rates. This can be achieved by:
-* Collecting a larger dataset of sign language gestures and annotating them with corresponding speech transcripts.
-* Experimenting with different machine learning models (e.g., convolutional neural networks, recurrent neural networks) to find the most effective approach for recognizing hand gestures.
-* Implementing data augmentation techniques to increase the diversity of the training data and improve the model's robustness.
-By improving the accuracy of hand</t>
+          <t>Based on the scores, the weakest area is feasibility. Here are three actionable suggestions to improve it:
+1. **Conduct a thorough feasibility analysis**: Break down the project into smaller components, assess the technical and logistical challenges, and identify potential roadblocks to ensure a realistic project timeline and budget.
+2. **Explore existing hand gesture recognition libraries**: Investigate popular libraries such as OpenPose, MediaPipe, or TensorFlow's Hand Gesture Recognition, and integrate them into the project to reduce development time and increase accuracy.
+3. **Collaborate with experts in computer vision and AI**: Reach out to researchers or developers with experience in hand gesture recognition and real-time speech synthesis to gain valuable insights, provide feedback, and accelerate the development process.</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>3.43</v>
+        <v>3.05</v>
       </c>
       <c r="T6" t="n">
         <v>6</v>
@@ -1314,81 +1373,88 @@
       <c r="V6" t="n">
         <v>1</v>
       </c>
-      <c r="W6" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>3</v>
-      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG6" t="n">
         <v>3.55</v>
       </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="AE6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH6" t="n">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN6" t="n">
         <v>3.05</v>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Based on the scores provided, it seems that the project has a strong novelty and impact, but may require some improvement in feasibility and presentation. Here are three specific, actionable suggestions to address these weaknesses:
-1. **Feasibility: Improve Hand Gesture Recognition Accuracy**
-To increase the feasibility of the project, focus on refining the hand gesture recognition algorithm to achieve higher accuracy rates. This can be achieved by:
-* Collecting a larger dataset of sign language gestures and annotating them with corresponding speech transcripts.
-* Experimenting with different machine learning models (e.g., convolutional neural networks, recurrent neural networks) to find the most effective approach for recognizing hand gestures.
-* Implementing data augmentation techniques to increase the diversity of the training data and improve the model's robustness.
-By improving the accuracy of hand</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>96</v>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Based on the scores, the weakest area is feasibility. Here are three actionable suggestions to improve it:
+1. **Conduct a thorough feasibility analysis**: Break down the project into smaller components, assess the technical and logistical challenges, and identify potential roadblocks to ensure a realistic project timeline and budget.
+2. **Explore existing hand gesture recognition libraries**: Investigate popular libraries such as OpenPose, MediaPipe, or TensorFlow's Hand Gesture Recognition, and integrate them into the project to reduce development time and increase accuracy.
+3. **Collaborate with experts in computer vision and AI**: Reach out to researchers or developers with experience in hand gesture recognition and real-time speech synthesis to gain valuable insights, provide feedback, and accelerate the development process.</t>
+        </is>
       </c>
       <c r="AP6" t="n">
-        <v>72</v>
+        <v>0.5</v>
       </c>
       <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW6" t="n">
         <v>84</v>
       </c>
     </row>
@@ -1435,99 +1501,125 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M7" t="n">
         <v>2</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>43</v>
+        <v>4</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Based on the project scores, here are three actionable suggestions to improve the weakest areas:
+1. **Novelty**: Introduce a gamification element that incorporates AI-generated personalized brain teasers, increasing user engagement and motivation to participate in cognitive exercises.
+2. **Feasibility**: Develop a prototype with a smaller user base to test and refine the app's speech analysis and daily mood tracking features, reducing technical complexity and costs.
+3. **Presentation**: Create a more visually appealing and user-friendly interface by incorporating animations, interactive graphics, and clear typography, making the app more accessible and enjoyable for elderly users.</t>
+        </is>
       </c>
       <c r="S7" t="n">
-        <v>3.17</v>
+        <v>3.05</v>
       </c>
       <c r="T7" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>3.05</v>
-      </c>
+        <v>3.35</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Based on the project scores, here are three actionable suggestions to improve the weakest areas:
+1. **Novelty**: Introduce a gamification element that incorporates AI-generated personalized brain teasers, increasing user engagement and motivation to participate in cognitive exercises.
+2. **Feasibility**: Develop a prototype with a smaller user base to test and refine the app's speech analysis and daily mood tracking features, reducing technical complexity and costs.
+3. **Presentation**: Create a more visually appealing and user-friendly interface by incorporating animations, interactive graphics, and clear typography, making the app more accessible and enjoyable for elderly users.</t>
+        </is>
+      </c>
+      <c r="AP7" t="n">
         <v>0.65</v>
       </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>96</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>72</v>
-      </c>
       <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW7" t="n">
         <v>84</v>
       </c>
     </row>
@@ -1574,35 +1666,36 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Based on the project scores, I've identified the weakest area as feasibility (score: 3.0/4). Here are three specific, actionable suggestions to improve it:
-1. **Conduct a detailed cost-benefit analysis**: To increase feasibility, the team should conduct a thorough cost-benefit analysis to ensure that the project's costs are reasonable and justifiable. This includes estimating the costs of sensor deployment, data processing, SMS alert services, and maintenance. The team should also identify potential revenue streams, such as subscription fees for emergency services or advertising opportunities.
-2. **Develop a detailed technical roadmap**: To improve feasibility, the team should create a detailed technical roadmap that outlines the specific hardware and software components required to implement FloodSense. This includes specifying the types of sensors needed, data processing algorithms</t>
+          <t>Based on the scores, the weakest area is feasibility. Here are three specific, actionable suggestions to improve it:
+1. Conduct a thorough cost-benefit analysis to identify potential cost-saving measures, such as using open-source hardware or leveraging existing infrastructure.
+2. Develop a detailed project timeline and resource allocation plan to ensure the team can meet the 2-hour prediction timeline and deploy the system within the given timeframe.
+3. Research and explore existing IoT sensor networks and flood prediction systems to identify potential partnerships or collaborations that can reduce development time and costs.</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>3.53</v>
+        <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
         <v>1</v>
@@ -1610,77 +1703,88 @@
       <c r="V8" t="n">
         <v>1</v>
       </c>
-      <c r="W8" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>3</v>
-      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF8" t="n">
         <v>4</v>
       </c>
       <c r="AG8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Based on the project scores, I've identified the weakest area as feasibility (score: 3.0/4). Here are three specific, actionable suggestions to improve it:
-1. **Conduct a detailed cost-benefit analysis**: To increase feasibility, the team should conduct a thorough cost-benefit analysis to ensure that the project's costs are reasonable and justifiable. This includes estimating the costs of sensor deployment, data processing, SMS alert services, and maintenance. The team should also identify potential revenue streams, such as subscription fees for emergency services or advertising opportunities.
-2. **Develop a detailed technical roadmap**: To improve feasibility, the team should create a detailed technical roadmap that outlines the specific hardware and software components required to implement FloodSense. This includes specifying the types of sensors needed, data processing algorithms</t>
-        </is>
-      </c>
+        <v>3.5</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="n">
-        <v>0.35</v>
+        <v>3</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AM8" t="n">
         <v>2</v>
       </c>
       <c r="AN8" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>96</v>
+        <v>3.2</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Based on the scores, the weakest area is feasibility. Here are three specific, actionable suggestions to improve it:
+1. Conduct a thorough cost-benefit analysis to identify potential cost-saving measures, such as using open-source hardware or leveraging existing infrastructure.
+2. Develop a detailed project timeline and resource allocation plan to ensure the team can meet the 2-hour prediction timeline and deploy the system within the given timeframe.
+3. Research and explore existing IoT sensor networks and flood prediction systems to identify potential partnerships or collaborations that can reduce development time and costs.</t>
+        </is>
       </c>
       <c r="AP8" t="n">
-        <v>72</v>
+        <v>0.8</v>
       </c>
       <c r="AQ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW8" t="n">
         <v>84</v>
       </c>
     </row>
@@ -1727,28 +1831,29 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>18</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>3.32</v>
+        <v>2.7</v>
       </c>
       <c r="T9" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1756,70 +1861,81 @@
       <c r="V9" t="n">
         <v>0</v>
       </c>
-      <c r="W9" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>3</v>
-      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>3</v>
       </c>
       <c r="AE9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF9" t="n">
         <v>4</v>
       </c>
       <c r="AG9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>3.05</v>
-      </c>
+        <v>3.5</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL9" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AM9" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="AN9" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>96</v>
-      </c>
+        <v>2.55</v>
+      </c>
+      <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="n">
-        <v>72</v>
+        <v>0.95</v>
       </c>
       <c r="AQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>41</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW9" t="n">
         <v>84</v>
       </c>
     </row>
@@ -1866,35 +1982,36 @@
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N10" t="n">
         <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Based on the project scores, it seems that the feasibility score is the weakest area. Here are three specific, actionable suggestions to improve it:
-1. **Conduct a thorough cost-benefit analysis**: The current feasibility score of 3.0/4 suggests that there may be concerns about the project's scalability and maintainability. To address this, I recommend conducting a detailed cost-benefit analysis to identify potential costs associated with developing and maintaining the app, such as server infrastructure, data storage, and emergency response system integration. This will help the team understand the financial implications of their decisions and make informed choices about how to optimize the project's feasibility.
-2. **Develop a prototype for GPS tracking**: The current GPS tracking feature is not fully fleshed out, which may be contributing to the low feasibility</t>
+          <t>Based on the scores, the weakest area is feasibility. Here are three actionable suggestions to improve it:
+1. Conduct a thorough analysis of the phone's hardware and software capabilities to ensure the disguised panic button is feasible and reliable.
+2. Develop a prototype to test the GPS tracking and alert system to identify potential technical challenges and refine the design.
+3. Research and explore existing APIs and services that can simplify the integration of GPS tracking and emergency alert systems, reducing development time and complexity.</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>3.43</v>
+        <v>3.05</v>
       </c>
       <c r="T10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U10" t="n">
         <v>1</v>
@@ -1902,77 +2019,88 @@
       <c r="V10" t="n">
         <v>1</v>
       </c>
-      <c r="W10" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>3</v>
-      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>3</v>
       </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Based on the project scores, it seems that the feasibility score is the weakest area. Here are three specific, actionable suggestions to improve it:
-1. **Conduct a thorough cost-benefit analysis**: The current feasibility score of 3.0/4 suggests that there may be concerns about the project's scalability and maintainability. To address this, I recommend conducting a detailed cost-benefit analysis to identify potential costs associated with developing and maintaining the app, such as server infrastructure, data storage, and emergency response system integration. This will help the team understand the financial implications of their decisions and make informed choices about how to optimize the project's feasibility.
-2. **Develop a prototype for GPS tracking**: The current GPS tracking feature is not fully fleshed out, which may be contributing to the low feasibility</t>
-        </is>
-      </c>
+        <v>3.35</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="n">
-        <v>0.65</v>
+        <v>3</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AM10" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="AN10" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>96</v>
+        <v>2.55</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Based on the scores, the weakest area is feasibility. Here are three actionable suggestions to improve it:
+1. Conduct a thorough analysis of the phone's hardware and software capabilities to ensure the disguised panic button is feasible and reliable.
+2. Develop a prototype to test the GPS tracking and alert system to identify potential technical challenges and refine the design.
+3. Research and explore existing APIs and services that can simplify the integration of GPS tracking and emergency alert systems, reducing development time and complexity.</t>
+        </is>
       </c>
       <c r="AP10" t="n">
-        <v>72</v>
+        <v>0.8</v>
       </c>
       <c r="AQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW10" t="n">
         <v>84</v>
       </c>
     </row>
@@ -2019,7 +2147,7 @@
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M11" t="n">
         <v>3</v>
@@ -2031,23 +2159,24 @@
         <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Based on the project scores, I've identified the weakest area as feasibility (score: 3.0/4). Here are three specific, actionable suggestions to improve it:
-1. **Conduct a thorough cost-benefit analysis**: Identify potential costs associated with developing and maintaining the platform, such as server maintenance, bandwidth costs, and content creation expenses. Estimate these costs and weigh them against the expected benefits of the project, including the number of users, engagement rates, and potential revenue streams (e.g., sponsored content or affiliate partnerships). This analysis will help you refine your business model and make data-driven decisions to optimize feasibility.
-2. **Develop a detailed technical roadmap**: Break down the platform's development into smaller, manageable tasks, and create a timeline with milestones and deadlines. Identify potential technical challenges</t>
+          <t>Based on the scores, the weakest area is feasibility, with a score of 3.0/4. Here are three actionable suggestions to improve it:
+1. Conduct a thorough cost-benefit analysis to identify potential revenue streams and optimize the platform's monetization strategy to ensure scalability and sustainability.
+2. Develop a detailed technical roadmap with clear milestones and timelines to ensure the platform's development is feasible and achievable within the given timeframe.
+3. Create a prototype of the platform's core features to test and validate assumptions, reducing the risk of technical debt and ensuring the platform's feasibility before scaling up.</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>3.53</v>
+        <v>3.35</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
         <v>1</v>
@@ -2055,77 +2184,88 @@
       <c r="V11" t="n">
         <v>1</v>
       </c>
-      <c r="W11" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>3</v>
-      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH11" t="n">
         <v>3.35</v>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Based on the project scores, I've identified the weakest area as feasibility (score: 3.0/4). Here are three specific, actionable suggestions to improve it:
-1. **Conduct a thorough cost-benefit analysis**: Identify potential costs associated with developing and maintaining the platform, such as server maintenance, bandwidth costs, and content creation expenses. Estimate these costs and weigh them against the expected benefits of the project, including the number of users, engagement rates, and potential revenue streams (e.g., sponsored content or affiliate partnerships). This analysis will help you refine your business model and make data-driven decisions to optimize feasibility.
-2. **Develop a detailed technical roadmap**: Break down the platform's development into smaller, manageable tasks, and create a timeline with milestones and deadlines. Identify potential technical challenges</t>
-        </is>
-      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="n">
-        <v>0.35</v>
+        <v>3</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL11" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AM11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN11" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>96</v>
+        <v>2.85</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Based on the scores, the weakest area is feasibility, with a score of 3.0/4. Here are three actionable suggestions to improve it:
+1. Conduct a thorough cost-benefit analysis to identify potential revenue streams and optimize the platform's monetization strategy to ensure scalability and sustainability.
+2. Develop a detailed technical roadmap with clear milestones and timelines to ensure the platform's development is feasible and achievable within the given timeframe.
+3. Create a prototype of the platform's core features to test and validate assumptions, reducing the risk of technical debt and ensuring the platform's feasibility before scaling up.</t>
+        </is>
       </c>
       <c r="AP11" t="n">
-        <v>72</v>
+        <v>0.65</v>
       </c>
       <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW11" t="n">
         <v>84</v>
       </c>
     </row>
@@ -2172,99 +2312,111 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>14</v>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T12" t="n">
+        <v>12</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG12" t="n">
         <v>3.35</v>
       </c>
-      <c r="Q12" t="n">
-        <v>19</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T12" t="n">
-        <v>26</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1</v>
-      </c>
-      <c r="W12" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="AE12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>3.05</v>
-      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL12" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="AM12" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>96</v>
-      </c>
+        <v>2.85</v>
+      </c>
+      <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="n">
-        <v>72</v>
+        <v>0.65</v>
       </c>
       <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW12" t="n">
         <v>84</v>
       </c>
     </row>
@@ -2311,99 +2463,111 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N13" t="n">
         <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>15</v>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T13" t="n">
+        <v>27</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG13" t="n">
         <v>3.35</v>
       </c>
-      <c r="Q13" t="n">
-        <v>20</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T13" t="n">
-        <v>31</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1</v>
-      </c>
-      <c r="W13" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="AE13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH13" t="n">
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN13" t="n">
         <v>2.7</v>
       </c>
-      <c r="AJ13" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL13" t="n">
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS13" t="n">
         <v>23</v>
       </c>
-      <c r="AM13" t="n">
-        <v>33</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>96</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>72</v>
-      </c>
-      <c r="AQ13" t="n">
+      <c r="AT13" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW13" t="n">
         <v>84</v>
       </c>
     </row>
@@ -2450,113 +2614,111 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N14" t="n">
         <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>16</v>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T14" t="n">
+        <v>13</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG14" t="n">
         <v>3.35</v>
       </c>
-      <c r="Q14" t="n">
-        <v>21</v>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>Based on the project scores, I've identified the weakest area as feasibility (score: 3.0/4). Here are three specific, actionable suggestions to improve it:
-1. **Conduct a thorough analysis of existing APIs and data sources**: The project relies heavily on historical data and real-time API integrations. To improve feasibility, conduct a comprehensive review of available APIs for public transport data (e.g., Google Maps Transit API, OpenTripPlanner) and identify the most suitable ones for RouteIQ. This will help ensure that the team can integrate these APIs seamlessly and efficiently.
-2. **Develop a prototype using existing libraries and frameworks**: To demonstrate feasibility, create a working prototype of RouteIQ using existing libraries and frameworks (e.g., TensorFlow for machine learning, Flask or Django for web</t>
-        </is>
-      </c>
-      <c r="S14" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T14" t="n">
-        <v>9</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="AE14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Based on the project scores, I've identified the weakest area as feasibility (score: 3.0/4). Here are three specific, actionable suggestions to improve it:
-1. **Conduct a thorough analysis of existing APIs and data sources**: The project relies heavily on historical data and real-time API integrations. To improve feasibility, conduct a comprehensive review of available APIs for public transport data (e.g., Google Maps Transit API, OpenTripPlanner) and identify the most suitable ones for RouteIQ. This will help ensure that the team can integrate these APIs seamlessly and efficiently.
-2. **Develop a prototype using existing libraries and frameworks**: To demonstrate feasibility, create a working prototype of RouteIQ using existing libraries and frameworks (e.g., TensorFlow for machine learning, Flask or Django for web</t>
-        </is>
-      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL14" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AM14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AN14" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>96</v>
-      </c>
+        <v>2.85</v>
+      </c>
+      <c r="AO14" t="inlineStr"/>
       <c r="AP14" t="n">
-        <v>72</v>
+        <v>0.65</v>
       </c>
       <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW14" t="n">
         <v>84</v>
       </c>
     </row>
@@ -2606,25 +2768,26 @@
         <v>3</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N15" t="n">
         <v>3</v>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>9</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="T15" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -2632,35 +2795,27 @@
       <c r="V15" t="n">
         <v>1</v>
       </c>
-      <c r="W15" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>3</v>
-      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3</v>
       </c>
       <c r="AE15" t="n">
         <v>4</v>
@@ -2669,33 +2824,52 @@
         <v>3</v>
       </c>
       <c r="AG15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>3.15</v>
-      </c>
+        <v>3.35</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr"/>
       <c r="AJ15" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL15" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="AM15" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="AN15" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>96</v>
-      </c>
+        <v>2.65</v>
+      </c>
+      <c r="AO15" t="inlineStr"/>
       <c r="AP15" t="n">
-        <v>72</v>
+        <v>0.7</v>
       </c>
       <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW15" t="n">
         <v>84</v>
       </c>
     </row>
@@ -2742,119 +2916,111 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N16" t="n">
         <v>3</v>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>18</v>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T16" t="n">
+        <v>14</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG16" t="n">
         <v>3.35</v>
       </c>
-      <c r="Q16" t="n">
-        <v>22</v>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>Based on the scores provided, it seems that the project has a good foundation but needs improvement in terms of feasibility and impact. Here are three specific, actionable suggestions to address these weaknesses:
-1. **Feasibility: Conduct a thorough cost-benefit analysis**
-To improve the feasibility score, I recommend conducting a detailed cost-benefit analysis to ensure that the project is financially viable. This should include estimating the costs of sensor installation, maintenance, and software development, as well as potential revenue streams from parking fees or advertising. The team should also consider the potential impact on existing parking systems and infrastructure.
-Actionable step: Schedule a meeting with industry experts, conduct market research, and create a detailed financial plan to present at the next team meeting.
-2. **Impact: Identify key stakeholders and partnerships**
-To</t>
-        </is>
-      </c>
-      <c r="S16" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T16" t="n">
-        <v>10</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="AE16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Based on the scores provided, it seems that the project has a good foundation but needs improvement in terms of feasibility and impact. Here are three specific, actionable suggestions to address these weaknesses:
-1. **Feasibility: Conduct a thorough cost-benefit analysis**
-To improve the feasibility score, I recommend conducting a detailed cost-benefit analysis to ensure that the project is financially viable. This should include estimating the costs of sensor installation, maintenance, and software development, as well as potential revenue streams from parking fees or advertising. The team should also consider the potential impact on existing parking systems and infrastructure.
-Actionable step: Schedule a meeting with industry experts, conduct market research, and create a detailed financial plan to present at the next team meeting.
-2. **Impact: Identify key stakeholders and partnerships**
-To</t>
-        </is>
-      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL16" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AM16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AN16" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>96</v>
-      </c>
+        <v>2.85</v>
+      </c>
+      <c r="AO16" t="inlineStr"/>
       <c r="AP16" t="n">
-        <v>72</v>
+        <v>0.65</v>
       </c>
       <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW16" t="n">
         <v>84</v>
       </c>
     </row>
@@ -2904,25 +3070,26 @@
         <v>3</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P17" t="n">
-        <v>3.45</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>10</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="T17" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2930,35 +3097,27 @@
       <c r="V17" t="n">
         <v>1</v>
       </c>
-      <c r="W17" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>4</v>
-      </c>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3</v>
       </c>
       <c r="AE17" t="n">
         <v>3</v>
@@ -2969,31 +3128,50 @@
       <c r="AG17" t="n">
         <v>3</v>
       </c>
-      <c r="AH17" t="n">
-        <v>3</v>
-      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="n">
-        <v>0.45</v>
+        <v>3</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>37</v>
+      </c>
+      <c r="AS17" t="n">
         <v>43</v>
       </c>
-      <c r="AM17" t="n">
-        <v>25</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>96</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>72</v>
-      </c>
-      <c r="AQ17" t="n">
+      <c r="AT17" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW17" t="n">
         <v>84</v>
       </c>
     </row>
@@ -3040,28 +3218,29 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
         <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>45</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="T18" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -3069,35 +3248,27 @@
       <c r="V18" t="n">
         <v>1</v>
       </c>
-      <c r="W18" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z18" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>4</v>
-      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>3</v>
       </c>
       <c r="AE18" t="n">
         <v>3</v>
@@ -3106,33 +3277,52 @@
         <v>3</v>
       </c>
       <c r="AG18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN18" t="n">
         <v>2.65</v>
       </c>
-      <c r="AJ18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>42</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>96</v>
-      </c>
+      <c r="AO18" t="inlineStr"/>
       <c r="AP18" t="n">
-        <v>72</v>
+        <v>0.35</v>
       </c>
       <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW18" t="n">
         <v>84</v>
       </c>
     </row>
@@ -3182,7 +3372,7 @@
         <v>3</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N19" t="n">
         <v>2</v>
@@ -3191,16 +3381,17 @@
         <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.95</v>
+        <v>2.35</v>
       </c>
       <c r="Q19" t="n">
-        <v>40</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="T19" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -3208,70 +3399,81 @@
       <c r="V19" t="n">
         <v>1</v>
       </c>
-      <c r="W19" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>3</v>
-      </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG19" t="n">
         <v>2.6</v>
       </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="AE19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH19" t="n">
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN19" t="n">
         <v>2.65</v>
       </c>
-      <c r="AJ19" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
         <v>47</v>
       </c>
-      <c r="AM19" t="n">
-        <v>43</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>96</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>72</v>
-      </c>
-      <c r="AQ19" t="n">
+      <c r="AS19" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW19" t="n">
         <v>84</v>
       </c>
     </row>
@@ -3321,25 +3523,26 @@
         <v>3</v>
       </c>
       <c r="M20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
         <v>3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>41</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="T20" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -3347,35 +3550,27 @@
       <c r="V20" t="n">
         <v>1</v>
       </c>
-      <c r="W20" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>3</v>
-      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>3</v>
       </c>
       <c r="AE20" t="n">
         <v>3</v>
@@ -3384,33 +3579,52 @@
         <v>3</v>
       </c>
       <c r="AG20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN20" t="n">
         <v>2.65</v>
       </c>
-      <c r="AJ20" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
         <v>48</v>
       </c>
-      <c r="AM20" t="n">
-        <v>44</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>96</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>72</v>
-      </c>
-      <c r="AQ20" t="n">
+      <c r="AS20" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW20" t="n">
         <v>84</v>
       </c>
     </row>
@@ -3463,93 +3677,105 @@
         <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P21" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="Q21" t="n">
+        <v>44</v>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T21" t="n">
         <v>49</v>
       </c>
-      <c r="S21" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>49</v>
+      </c>
+      <c r="AS21" t="n">
         <v>50</v>
       </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1</v>
-      </c>
-      <c r="W21" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="AE21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>49</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>50</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>96</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>72</v>
-      </c>
-      <c r="AQ21" t="n">
+      <c r="AT21" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW21" t="n">
         <v>84</v>
       </c>
     </row>
@@ -3596,99 +3822,111 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N22" t="n">
         <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P22" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="Q22" t="n">
-        <v>23</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="T22" t="n">
+        <v>30</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
         <v>39</v>
       </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1</v>
-      </c>
-      <c r="W22" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z22" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="AE22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>45</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>96</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>72</v>
-      </c>
-      <c r="AQ22" t="n">
+      <c r="AS22" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW22" t="n">
         <v>84</v>
       </c>
     </row>
@@ -3735,10 +3973,10 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N23" t="n">
         <v>2</v>
@@ -3747,16 +3985,17 @@
         <v>2</v>
       </c>
       <c r="P23" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>50</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="T23" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -3764,35 +4003,27 @@
       <c r="V23" t="n">
         <v>1</v>
       </c>
-      <c r="W23" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z23" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>4</v>
-      </c>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3</v>
       </c>
       <c r="AE23" t="n">
         <v>3</v>
@@ -3801,33 +4032,52 @@
         <v>3</v>
       </c>
       <c r="AG23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN23" t="n">
         <v>2.65</v>
       </c>
-      <c r="AJ23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>45</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>46</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>96</v>
-      </c>
+      <c r="AO23" t="inlineStr"/>
       <c r="AP23" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="AQ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW23" t="n">
         <v>84</v>
       </c>
     </row>
@@ -3874,10 +4124,10 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N24" t="n">
         <v>3</v>
@@ -3886,16 +4136,17 @@
         <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>36</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="T24" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -3903,70 +4154,81 @@
       <c r="V24" t="n">
         <v>1</v>
       </c>
-      <c r="W24" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z24" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>3</v>
-      </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>3</v>
       </c>
       <c r="AE24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF24" t="n">
         <v>3</v>
       </c>
       <c r="AG24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH24" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN24" t="n">
         <v>2.65</v>
       </c>
-      <c r="AJ24" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>39</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>47</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>96</v>
-      </c>
+      <c r="AO24" t="inlineStr"/>
       <c r="AP24" t="n">
-        <v>72</v>
+        <v>0.7</v>
       </c>
       <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>31</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW24" t="n">
         <v>84</v>
       </c>
     </row>
@@ -4013,28 +4275,29 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
       </c>
       <c r="P25" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="Q25" t="n">
-        <v>46</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="T25" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -4042,38 +4305,30 @@
       <c r="V25" t="n">
         <v>1</v>
       </c>
-      <c r="W25" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z25" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>3</v>
-      </c>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF25" t="n">
         <v>3</v>
@@ -4081,31 +4336,50 @@
       <c r="AG25" t="n">
         <v>3</v>
       </c>
-      <c r="AH25" t="n">
-        <v>2.7</v>
-      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="n">
-        <v>0.65</v>
+        <v>2</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL25" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="AM25" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AN25" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>96</v>
-      </c>
+        <v>2.65</v>
+      </c>
+      <c r="AO25" t="inlineStr"/>
       <c r="AP25" t="n">
-        <v>72</v>
+        <v>0.35</v>
       </c>
       <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>41</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW25" t="n">
         <v>84</v>
       </c>
     </row>
@@ -4155,7 +4429,7 @@
         <v>3</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N26" t="n">
         <v>3</v>
@@ -4164,16 +4438,17 @@
         <v>3</v>
       </c>
       <c r="P26" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="Q26" t="n">
-        <v>34</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="R26" t="inlineStr"/>
       <c r="S26" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="T26" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -4181,70 +4456,81 @@
       <c r="V26" t="n">
         <v>1</v>
       </c>
-      <c r="W26" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>3</v>
-      </c>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3</v>
       </c>
       <c r="AE26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>3.05</v>
-      </c>
+        <v>3.35</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL26" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="AM26" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="AN26" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>96</v>
-      </c>
+        <v>2.7</v>
+      </c>
+      <c r="AO26" t="inlineStr"/>
       <c r="AP26" t="n">
-        <v>72</v>
+        <v>0.65</v>
       </c>
       <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW26" t="n">
         <v>84</v>
       </c>
     </row>
@@ -4291,35 +4577,36 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N27" t="n">
         <v>4</v>
       </c>
       <c r="O27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P27" t="n">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="Q27" t="n">
         <v>6</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Based on the scores, it seems that BlindNav has a strong novelty score but may struggle with feasibility and impact. Here are three actionable suggestions to improve the project:
-1. **Refine the obstacle detection algorithm**: The current phone camera-based approach might not be robust enough for various environments and lighting conditions. Consider exploring alternative methods such as lidar or sonar sensors, which could provide more accurate and reliable data. Additionally, investigate machine learning techniques like object detection and segmentation to improve the accuracy of obstacle detection.
-2. **Enhance signboard recognition and interpretation**: While reading aloud signboards is a great feature, it's essential to ensure that the system can accurately interpret the content and provide relevant information to users. Consider incorporating natural language processing (NLP) techniques to better understand the context and meaning</t>
+          <t>Based on the scores, the weakest area is feasibility, with a score of 2.0/4. Here are three actionable suggestions to improve it:
+1. **Conduct a thorough cost-benefit analysis**: Assess the feasibility of using a phone camera, processing power, and audio output to detect obstacles and read signboards, ensuring it's cost-effective and practical for widespread adoption.
+2. **Explore alternative hardware solutions**: Consider using specialized hardware, such as ultrasonic sensors or lidar, to improve obstacle detection accuracy and reduce reliance on phone camera capabilities.
+3. **Develop a prototype with a smaller team**: Build a minimal viable prototype (MVP) with a smaller team to test and refine the project's technical feasibility before scaling up to a full team and production-ready implementation.</t>
         </is>
       </c>
       <c r="S27" t="n">
-        <v>3.43</v>
+        <v>3.2</v>
       </c>
       <c r="T27" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U27" t="n">
         <v>1</v>
@@ -4327,77 +4614,88 @@
       <c r="V27" t="n">
         <v>0</v>
       </c>
-      <c r="W27" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>3</v>
-      </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG27" t="n">
         <v>3.55</v>
       </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="AE27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Based on the scores, it seems that BlindNav has a strong novelty score but may struggle with feasibility and impact. Here are three actionable suggestions to improve the project:
-1. **Refine the obstacle detection algorithm**: The current phone camera-based approach might not be robust enough for various environments and lighting conditions. Consider exploring alternative methods such as lidar or sonar sensors, which could provide more accurate and reliable data. Additionally, investigate machine learning techniques like object detection and segmentation to improve the accuracy of obstacle detection.
-2. **Enhance signboard recognition and interpretation**: While reading aloud signboards is a great feature, it's essential to ensure that the system can accurately interpret the content and provide relevant information to users. Consider incorporating natural language processing (NLP) techniques to better understand the context and meaning</t>
-        </is>
-      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="n">
-        <v>0.65</v>
+        <v>3</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL27" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="AM27" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="AN27" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>96</v>
+        <v>3.2</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Based on the scores, the weakest area is feasibility, with a score of 2.0/4. Here are three actionable suggestions to improve it:
+1. **Conduct a thorough cost-benefit analysis**: Assess the feasibility of using a phone camera, processing power, and audio output to detect obstacles and read signboards, ensuring it's cost-effective and practical for widespread adoption.
+2. **Explore alternative hardware solutions**: Consider using specialized hardware, such as ultrasonic sensors or lidar, to improve obstacle detection accuracy and reduce reliance on phone camera capabilities.
+3. **Develop a prototype with a smaller team**: Build a minimal viable prototype (MVP) with a smaller team to test and refine the project's technical feasibility before scaling up to a full team and production-ready implementation.</t>
+        </is>
       </c>
       <c r="AP27" t="n">
-        <v>72</v>
+        <v>0.5</v>
       </c>
       <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW27" t="n">
         <v>84</v>
       </c>
     </row>
@@ -4447,25 +4745,26 @@
         <v>3</v>
       </c>
       <c r="M28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N28" t="n">
         <v>3</v>
       </c>
       <c r="O28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P28" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>11</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>3.27</v>
+        <v>2.7</v>
       </c>
       <c r="T28" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -4473,70 +4772,81 @@
       <c r="V28" t="n">
         <v>1</v>
       </c>
-      <c r="W28" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>3</v>
-      </c>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG28" t="n">
         <v>3.35</v>
       </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="AE28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>3</v>
-      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr"/>
       <c r="AJ28" t="n">
-        <v>0.45</v>
+        <v>2</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL28" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="AM28" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="AN28" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>96</v>
-      </c>
+        <v>2.65</v>
+      </c>
+      <c r="AO28" t="inlineStr"/>
       <c r="AP28" t="n">
-        <v>72</v>
+        <v>0.7</v>
       </c>
       <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>33</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW28" t="n">
         <v>84</v>
       </c>
     </row>
@@ -4583,99 +4893,111 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N29" t="n">
         <v>3</v>
       </c>
       <c r="O29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>26</v>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T29" t="n">
+        <v>15</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG29" t="n">
         <v>3.35</v>
       </c>
-      <c r="Q29" t="n">
-        <v>24</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T29" t="n">
-        <v>32</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1</v>
-      </c>
-      <c r="W29" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z29" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="AE29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>2.7</v>
-      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr"/>
       <c r="AJ29" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="AK29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL29" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="AM29" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="AN29" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>96</v>
-      </c>
+        <v>2.85</v>
+      </c>
+      <c r="AO29" t="inlineStr"/>
       <c r="AP29" t="n">
-        <v>72</v>
+        <v>0.65</v>
       </c>
       <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW29" t="n">
         <v>84</v>
       </c>
     </row>
@@ -4722,35 +5044,36 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N30" t="n">
         <v>4</v>
       </c>
       <c r="O30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="Q30" t="n">
         <v>7</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Based on the scores provided, it seems that Feasibility is the weakest area of the project. Here are three specific, actionable suggestions to improve it:
-1. **Conduct a detailed cost-benefit analysis**: Provide a thorough breakdown of the estimated costs associated with developing and manufacturing the IoT device, including materials, production, and distribution expenses. This will help demonstrate that the project's goals can be achieved within a reasonable budget. Consider using publicly available data on similar IoT projects to support your estimates.
-2. **Identify potential manufacturing partners**: Research and identify companies that specialize in low-cost, high-volume manufacturing of electronic devices. Reach out to these partners to discuss potential collaboration opportunities, such as co-branding or joint production. This will help reduce the project's financial burden and increase its feasibility.</t>
+          <t>Based on the scores, the weakest area is feasibility. Here are three actionable suggestions to improve it:
+1. **Conduct a detailed cost-benefit analysis**: Estimate the production cost of the device, material costs, and potential revenue streams to ensure the project is financially viable.
+2. **Research and identify cost-effective manufacturing options**: Explore 3D printing, PCB assembly, or other cost-effective manufacturing methods to reduce production costs.
+3. **Collaborate with existing IoT device manufacturers**: Partner with companies that already produce IoT devices to leverage their expertise, reduce development time, and lower costs.</t>
         </is>
       </c>
       <c r="S30" t="n">
-        <v>3.53</v>
+        <v>3.05</v>
       </c>
       <c r="T30" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="U30" t="n">
         <v>1</v>
@@ -4758,77 +5081,88 @@
       <c r="V30" t="n">
         <v>0</v>
       </c>
-      <c r="W30" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z30" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>3</v>
-      </c>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG30" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH30" t="n">
         <v>3.35</v>
       </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Based on the scores provided, it seems that Feasibility is the weakest area of the project. Here are three specific, actionable suggestions to improve it:
-1. **Conduct a detailed cost-benefit analysis**: Provide a thorough breakdown of the estimated costs associated with developing and manufacturing the IoT device, including materials, production, and distribution expenses. This will help demonstrate that the project's goals can be achieved within a reasonable budget. Consider using publicly available data on similar IoT projects to support your estimates.
-2. **Identify potential manufacturing partners**: Research and identify companies that specialize in low-cost, high-volume manufacturing of electronic devices. Reach out to these partners to discuss potential collaboration opportunities, such as co-branding or joint production. This will help reduce the project's financial burden and increase its feasibility.</t>
-        </is>
-      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr"/>
       <c r="AJ30" t="n">
-        <v>0.35</v>
+        <v>3</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL30" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="AM30" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AN30" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>96</v>
+        <v>2.55</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Based on the scores, the weakest area is feasibility. Here are three actionable suggestions to improve it:
+1. **Conduct a detailed cost-benefit analysis**: Estimate the production cost of the device, material costs, and potential revenue streams to ensure the project is financially viable.
+2. **Research and identify cost-effective manufacturing options**: Explore 3D printing, PCB assembly, or other cost-effective manufacturing methods to reduce production costs.
+3. **Collaborate with existing IoT device manufacturers**: Partner with companies that already produce IoT devices to leverage their expertise, reduce development time, and lower costs.</t>
+        </is>
       </c>
       <c r="AP30" t="n">
-        <v>72</v>
+        <v>0.8</v>
       </c>
       <c r="AQ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW30" t="n">
         <v>84</v>
       </c>
     </row>
@@ -4875,25 +5209,26 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N31" t="n">
         <v>3</v>
       </c>
       <c r="O31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P31" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>25</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
-        <v>3.13</v>
+        <v>2.7</v>
       </c>
       <c r="T31" t="n">
         <v>35</v>
@@ -4904,70 +5239,81 @@
       <c r="V31" t="n">
         <v>1</v>
       </c>
-      <c r="W31" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z31" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>3</v>
-      </c>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG31" t="n">
         <v>3.35</v>
       </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="AE31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>2.7</v>
-      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr"/>
       <c r="AJ31" t="n">
-        <v>0.65</v>
+        <v>2</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL31" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="AM31" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="AN31" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>96</v>
-      </c>
+        <v>2.65</v>
+      </c>
+      <c r="AO31" t="inlineStr"/>
       <c r="AP31" t="n">
-        <v>72</v>
+        <v>0.7</v>
       </c>
       <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW31" t="n">
         <v>84</v>
       </c>
     </row>
@@ -5017,7 +5363,7 @@
         <v>3</v>
       </c>
       <c r="M32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N32" t="n">
         <v>3</v>
@@ -5026,16 +5372,17 @@
         <v>3</v>
       </c>
       <c r="P32" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="Q32" t="n">
-        <v>35</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="R32" t="inlineStr"/>
       <c r="S32" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="T32" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -5043,35 +5390,27 @@
       <c r="V32" t="n">
         <v>1</v>
       </c>
-      <c r="W32" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z32" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>4</v>
-      </c>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>3</v>
       </c>
       <c r="AE32" t="n">
         <v>3</v>
@@ -5080,33 +5419,52 @@
         <v>3</v>
       </c>
       <c r="AG32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN32" t="n">
         <v>2.85</v>
       </c>
-      <c r="AJ32" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>31</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>96</v>
-      </c>
+      <c r="AO32" t="inlineStr"/>
       <c r="AP32" t="n">
-        <v>72</v>
+        <v>0.3</v>
       </c>
       <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>42</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW32" t="n">
         <v>84</v>
       </c>
     </row>
@@ -5153,28 +5511,29 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N33" t="n">
         <v>3</v>
       </c>
       <c r="O33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="Q33" t="n">
-        <v>26</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>3.23</v>
+        <v>2.85</v>
       </c>
       <c r="T33" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -5182,70 +5541,81 @@
       <c r="V33" t="n">
         <v>1</v>
       </c>
-      <c r="W33" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z33" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>3</v>
-      </c>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG33" t="n">
         <v>3.65</v>
       </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="AE33" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>2.7</v>
-      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr"/>
       <c r="AJ33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="n">
         <v>0.95</v>
       </c>
-      <c r="AK33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>37</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>96</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>72</v>
-      </c>
       <c r="AQ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW33" t="n">
         <v>84</v>
       </c>
     </row>
@@ -5292,99 +5662,111 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N34" t="n">
         <v>3</v>
       </c>
       <c r="O34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>30</v>
+      </c>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T34" t="n">
+        <v>18</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG34" t="n">
         <v>3.35</v>
       </c>
-      <c r="Q34" t="n">
-        <v>27</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T34" t="n">
-        <v>11</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1</v>
-      </c>
-      <c r="W34" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z34" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="AE34" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>3.35</v>
-      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr"/>
       <c r="AJ34" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL34" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="AM34" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AN34" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>96</v>
-      </c>
+        <v>2.85</v>
+      </c>
+      <c r="AO34" t="inlineStr"/>
       <c r="AP34" t="n">
-        <v>72</v>
+        <v>0.65</v>
       </c>
       <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW34" t="n">
         <v>84</v>
       </c>
     </row>
@@ -5431,28 +5813,29 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P35" t="n">
-        <v>3.45</v>
+        <v>2</v>
       </c>
       <c r="Q35" t="n">
-        <v>12</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>3.13</v>
+        <v>2.65</v>
       </c>
       <c r="T35" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -5460,70 +5843,81 @@
       <c r="V35" t="n">
         <v>1</v>
       </c>
-      <c r="W35" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z35" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>3</v>
-      </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>3</v>
       </c>
       <c r="AE35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG35" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN35" t="n">
         <v>2.65</v>
       </c>
-      <c r="AJ35" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>48</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>96</v>
-      </c>
+      <c r="AO35" t="inlineStr"/>
       <c r="AP35" t="n">
-        <v>72</v>
+        <v>1.5</v>
       </c>
       <c r="AQ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>35</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW35" t="n">
         <v>84</v>
       </c>
     </row>
@@ -5573,25 +5967,26 @@
         <v>3</v>
       </c>
       <c r="M36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N36" t="n">
         <v>3</v>
       </c>
       <c r="O36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P36" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="Q36" t="n">
-        <v>13</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
-        <v>3.17</v>
+        <v>2.85</v>
       </c>
       <c r="T36" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -5599,38 +5994,30 @@
       <c r="V36" t="n">
         <v>1</v>
       </c>
-      <c r="W36" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z36" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>3</v>
-      </c>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD36" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>3</v>
       </c>
       <c r="AE36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF36" t="n">
         <v>3</v>
@@ -5638,31 +6025,50 @@
       <c r="AG36" t="n">
         <v>3</v>
       </c>
-      <c r="AH36" t="n">
-        <v>2.7</v>
-      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr"/>
       <c r="AJ36" t="n">
-        <v>0.75</v>
+        <v>3</v>
       </c>
       <c r="AK36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL36" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="AM36" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="AN36" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>96</v>
-      </c>
+        <v>2.85</v>
+      </c>
+      <c r="AO36" t="inlineStr"/>
       <c r="AP36" t="n">
-        <v>72</v>
+        <v>0.3</v>
       </c>
       <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>43</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW36" t="n">
         <v>84</v>
       </c>
     </row>
@@ -5709,28 +6115,29 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N37" t="n">
         <v>3</v>
       </c>
       <c r="O37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P37" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="Q37" t="n">
-        <v>28</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>3.13</v>
+        <v>2.7</v>
       </c>
       <c r="T37" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -5738,38 +6145,30 @@
       <c r="V37" t="n">
         <v>1</v>
       </c>
-      <c r="W37" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z37" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>3</v>
-      </c>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>3</v>
       </c>
       <c r="AE37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF37" t="n">
         <v>3</v>
@@ -5777,31 +6176,50 @@
       <c r="AG37" t="n">
         <v>3</v>
       </c>
-      <c r="AH37" t="n">
-        <v>2.7</v>
-      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr"/>
       <c r="AJ37" t="n">
-        <v>0.65</v>
+        <v>3</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL37" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="AM37" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="AN37" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>96</v>
-      </c>
+        <v>2.55</v>
+      </c>
+      <c r="AO37" t="inlineStr"/>
       <c r="AP37" t="n">
-        <v>72</v>
+        <v>0.45</v>
       </c>
       <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>44</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>45</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW37" t="n">
         <v>84</v>
       </c>
     </row>
@@ -5851,25 +6269,26 @@
         <v>3</v>
       </c>
       <c r="M38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N38" t="n">
         <v>3</v>
       </c>
       <c r="O38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P38" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="Q38" t="n">
-        <v>14</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>3.27</v>
+        <v>2.85</v>
       </c>
       <c r="T38" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -5877,35 +6296,27 @@
       <c r="V38" t="n">
         <v>1</v>
       </c>
-      <c r="W38" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z38" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>3</v>
-      </c>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>3</v>
       </c>
       <c r="AE38" t="n">
         <v>3</v>
@@ -5916,31 +6327,50 @@
       <c r="AG38" t="n">
         <v>3</v>
       </c>
-      <c r="AH38" t="n">
-        <v>3</v>
-      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr"/>
       <c r="AJ38" t="n">
-        <v>0.45</v>
+        <v>3</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL38" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="AM38" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="AN38" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>96</v>
-      </c>
+        <v>2.85</v>
+      </c>
+      <c r="AO38" t="inlineStr"/>
       <c r="AP38" t="n">
-        <v>72</v>
+        <v>0.3</v>
       </c>
       <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>45</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW38" t="n">
         <v>84</v>
       </c>
     </row>
@@ -5996,19 +6426,20 @@
         <v>3</v>
       </c>
       <c r="O39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P39" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="Q39" t="n">
-        <v>47</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="T39" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -6016,70 +6447,81 @@
       <c r="V39" t="n">
         <v>1</v>
       </c>
-      <c r="W39" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z39" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>3</v>
-      </c>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG39" t="n">
         <v>3.35</v>
       </c>
-      <c r="AD39" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="AE39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>2.7</v>
-      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr"/>
       <c r="AJ39" t="n">
-        <v>0.65</v>
+        <v>3</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL39" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="AM39" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="AN39" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>96</v>
-      </c>
+        <v>2.55</v>
+      </c>
+      <c r="AO39" t="inlineStr"/>
       <c r="AP39" t="n">
-        <v>72</v>
+        <v>0.8</v>
       </c>
       <c r="AQ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>46</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW39" t="n">
         <v>84</v>
       </c>
     </row>
@@ -6129,7 +6571,7 @@
         <v>3</v>
       </c>
       <c r="M40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N40" t="n">
         <v>2</v>
@@ -6138,87 +6580,99 @@
         <v>3</v>
       </c>
       <c r="P40" t="n">
-        <v>2.95</v>
+        <v>2.35</v>
       </c>
       <c r="Q40" t="n">
-        <v>42</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="T40" t="n">
+        <v>50</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AO40" t="inlineStr"/>
+      <c r="AP40" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS40" t="n">
         <v>49</v>
       </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1</v>
-      </c>
-      <c r="W40" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z40" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD40" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="AE40" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>49</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>96</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>72</v>
-      </c>
-      <c r="AQ40" t="n">
+      <c r="AT40" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW40" t="n">
         <v>84</v>
       </c>
     </row>
@@ -6268,25 +6722,26 @@
         <v>3</v>
       </c>
       <c r="M41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P41" t="n">
-        <v>3.45</v>
+        <v>2.35</v>
       </c>
       <c r="Q41" t="n">
-        <v>15</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="R41" t="inlineStr"/>
       <c r="S41" t="n">
-        <v>3.27</v>
+        <v>2.65</v>
       </c>
       <c r="T41" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -6294,35 +6749,27 @@
       <c r="V41" t="n">
         <v>1</v>
       </c>
-      <c r="W41" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z41" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>3</v>
-      </c>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD41" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>3</v>
       </c>
       <c r="AE41" t="n">
         <v>3</v>
@@ -6333,31 +6780,50 @@
       <c r="AG41" t="n">
         <v>3</v>
       </c>
-      <c r="AH41" t="n">
-        <v>3</v>
-      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr"/>
       <c r="AJ41" t="n">
-        <v>0.45</v>
+        <v>2</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL41" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="AM41" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="AN41" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>96</v>
-      </c>
+        <v>2.65</v>
+      </c>
+      <c r="AO41" t="inlineStr"/>
       <c r="AP41" t="n">
-        <v>72</v>
+        <v>0.65</v>
       </c>
       <c r="AQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>46</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW41" t="n">
         <v>84</v>
       </c>
     </row>
@@ -6404,99 +6870,125 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N42" t="n">
         <v>3</v>
       </c>
       <c r="O42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P42" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="Q42" t="n">
-        <v>29</v>
+        <v>35</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Based on the scores, the weakest area is feasibility. Here are three actionable suggestions to improve it:
+1. Conduct a thorough review of existing satellite imagery analysis tools and APIs to identify potential integration points for GreenRoof AI.
+2. Develop a detailed technical roadmap outlining the feasibility of integrating machine learning models with satellite data and existing building information systems.
+3. Research and gather case studies of existing rooftop solar panel installations to validate the feasibility of GreenRoof AI's proposed approach.</t>
+        </is>
       </c>
       <c r="S42" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="T42" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V42" t="n">
-        <v>1</v>
-      </c>
-      <c r="W42" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z42" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD42" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>3.5</v>
       </c>
       <c r="AE42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF42" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AG42" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>3.05</v>
-      </c>
+        <v>3.58</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr"/>
       <c r="AJ42" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL42" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="AM42" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="AN42" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>96</v>
+        <v>3.2</v>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Based on the scores, the weakest area is feasibility. Here are three actionable suggestions to improve it:
+1. Conduct a thorough review of existing satellite imagery analysis tools and APIs to identify potential integration points for GreenRoof AI.
+2. Develop a detailed technical roadmap outlining the feasibility of integrating machine learning models with satellite data and existing building information systems.
+3. Research and gather case studies of existing rooftop solar panel installations to validate the feasibility of GreenRoof AI's proposed approach.</t>
+        </is>
       </c>
       <c r="AP42" t="n">
-        <v>72</v>
+        <v>0.88</v>
       </c>
       <c r="AQ42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW42" t="n">
         <v>84</v>
       </c>
     </row>
@@ -6543,99 +7035,111 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N43" t="n">
         <v>3</v>
       </c>
       <c r="O43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P43" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>36</v>
+      </c>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T43" t="n">
+        <v>38</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG43" t="n">
         <v>3.35</v>
       </c>
-      <c r="Q43" t="n">
-        <v>30</v>
-      </c>
-      <c r="S43" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="T43" t="n">
-        <v>15</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1</v>
-      </c>
-      <c r="W43" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z43" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD43" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="AE43" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>3.05</v>
-      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr"/>
       <c r="AJ43" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL43" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="AM43" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="AN43" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO43" t="n">
-        <v>96</v>
-      </c>
+        <v>2.55</v>
+      </c>
+      <c r="AO43" t="inlineStr"/>
       <c r="AP43" t="n">
-        <v>72</v>
+        <v>0.8</v>
       </c>
       <c r="AQ43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>47</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW43" t="n">
         <v>84</v>
       </c>
     </row>
@@ -6682,99 +7186,111 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N44" t="n">
         <v>3</v>
       </c>
       <c r="O44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P44" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>37</v>
+      </c>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T44" t="n">
+        <v>39</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG44" t="n">
         <v>3.35</v>
       </c>
-      <c r="Q44" t="n">
-        <v>31</v>
-      </c>
-      <c r="S44" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="T44" t="n">
-        <v>12</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1</v>
-      </c>
-      <c r="W44" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z44" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD44" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="AE44" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>3.35</v>
-      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr"/>
       <c r="AJ44" t="n">
-        <v>0.05</v>
+        <v>2</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL44" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="AM44" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AN44" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>96</v>
-      </c>
+        <v>2.65</v>
+      </c>
+      <c r="AO44" t="inlineStr"/>
       <c r="AP44" t="n">
-        <v>72</v>
+        <v>0.7</v>
       </c>
       <c r="AQ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>37</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW44" t="n">
         <v>84</v>
       </c>
     </row>
@@ -6821,99 +7337,111 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N45" t="n">
         <v>3</v>
       </c>
       <c r="O45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P45" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="Q45" t="n">
+        <v>38</v>
+      </c>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T45" t="n">
+        <v>40</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr"/>
+      <c r="AJ45" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AO45" t="inlineStr"/>
+      <c r="AP45" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS45" t="n">
         <v>48</v>
       </c>
-      <c r="S45" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T45" t="n">
-        <v>45</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1</v>
-      </c>
-      <c r="W45" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z45" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD45" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="AE45" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>25</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>41</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>96</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>72</v>
-      </c>
-      <c r="AQ45" t="n">
+      <c r="AT45" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW45" t="n">
         <v>84</v>
       </c>
     </row>
@@ -6960,7 +7488,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M46" t="n">
         <v>2</v>
@@ -6972,16 +7500,17 @@
         <v>3</v>
       </c>
       <c r="P46" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="Q46" t="n">
-        <v>44</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="R46" t="inlineStr"/>
       <c r="S46" t="n">
-        <v>3.27</v>
+        <v>2.85</v>
       </c>
       <c r="T46" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -6989,70 +7518,81 @@
       <c r="V46" t="n">
         <v>1</v>
       </c>
-      <c r="W46" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z46" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>3</v>
-      </c>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>3</v>
       </c>
       <c r="AE46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG46" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH46" t="n">
         <v>3.35</v>
       </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr"/>
       <c r="AJ46" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AO46" t="inlineStr"/>
+      <c r="AP46" t="n">
         <v>0.65</v>
       </c>
-      <c r="AK46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>20</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>9</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>96</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>72</v>
-      </c>
       <c r="AQ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>31</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW46" t="n">
         <v>84</v>
       </c>
     </row>
@@ -7099,99 +7639,111 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N47" t="n">
         <v>3</v>
       </c>
       <c r="O47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P47" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>40</v>
+      </c>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T47" t="n">
+        <v>22</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG47" t="n">
         <v>3.35</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AO47" t="inlineStr"/>
+      <c r="AP47" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR47" t="n">
         <v>32</v>
       </c>
-      <c r="S47" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="T47" t="n">
-        <v>16</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1</v>
-      </c>
-      <c r="W47" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z47" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD47" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="AE47" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>21</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>23</v>
-      </c>
-      <c r="AN47" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO47" t="n">
-        <v>96</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>72</v>
-      </c>
-      <c r="AQ47" t="n">
+      <c r="AS47" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW47" t="n">
         <v>84</v>
       </c>
     </row>
@@ -7238,99 +7790,111 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N48" t="n">
         <v>3</v>
       </c>
       <c r="O48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P48" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>41</v>
+      </c>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T48" t="n">
+        <v>41</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG48" t="n">
         <v>3.35</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AO48" t="inlineStr"/>
+      <c r="AP48" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR48" t="n">
         <v>33</v>
       </c>
-      <c r="S48" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T48" t="n">
-        <v>19</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1</v>
-      </c>
-      <c r="W48" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z48" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD48" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="AE48" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>35</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>10</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>96</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>72</v>
-      </c>
-      <c r="AQ48" t="n">
+      <c r="AS48" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW48" t="n">
         <v>84</v>
       </c>
     </row>
@@ -7377,99 +7941,125 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
       </c>
       <c r="P49" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="Q49" t="n">
-        <v>37</v>
+        <v>8</v>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Based on the scores, VirtualLab seems to be a promising project. Here are three actionable suggestions to improve the weakest areas:
+1. **Novelty**: Introduce a unique "Experiment of the Week" feature, where users can participate in a new, interactive experiment every week, showcasing the platform's adaptability and staying power.
+2. **Feasibility**: Optimize the platform's performance by leveraging WebAssembly or WebGL for smoother 3D simulations, reducing loading times and improving overall user experience.
+3. **Presentation**: Create a visually appealing dashboard to display lab results, including interactive graphs, charts, and infographics, making it easier for users to understand and analyze their experiment outcomes.</t>
+        </is>
       </c>
       <c r="S49" t="n">
-        <v>3.27</v>
+        <v>3.05</v>
       </c>
       <c r="T49" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V49" t="n">
-        <v>1</v>
-      </c>
-      <c r="W49" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z49" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD49" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>3</v>
       </c>
       <c r="AE49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG49" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>3.05</v>
-      </c>
+        <v>3.35</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr"/>
       <c r="AJ49" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL49" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="AM49" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="AN49" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>96</v>
+        <v>3</v>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Based on the scores, VirtualLab seems to be a promising project. Here are three actionable suggestions to improve the weakest areas:
+1. **Novelty**: Introduce a unique "Experiment of the Week" feature, where users can participate in a new, interactive experiment every week, showcasing the platform's adaptability and staying power.
+2. **Feasibility**: Optimize the platform's performance by leveraging WebAssembly or WebGL for smoother 3D simulations, reducing loading times and improving overall user experience.
+3. **Presentation**: Create a visually appealing dashboard to display lab results, including interactive graphs, charts, and infographics, making it easier for users to understand and analyze their experiment outcomes.</t>
+        </is>
       </c>
       <c r="AP49" t="n">
-        <v>72</v>
+        <v>0.35</v>
       </c>
       <c r="AQ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW49" t="n">
         <v>84</v>
       </c>
     </row>
@@ -7519,25 +8109,26 @@
         <v>3</v>
       </c>
       <c r="M50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N50" t="n">
         <v>3</v>
       </c>
       <c r="O50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P50" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="Q50" t="n">
-        <v>16</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="R50" t="inlineStr"/>
       <c r="S50" t="n">
-        <v>3.27</v>
+        <v>2.85</v>
       </c>
       <c r="T50" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -7545,70 +8136,81 @@
       <c r="V50" t="n">
         <v>1</v>
       </c>
-      <c r="W50" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z50" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>3</v>
-      </c>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG50" t="n">
         <v>3.35</v>
       </c>
-      <c r="AD50" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="AE50" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>3</v>
-      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr"/>
       <c r="AJ50" t="n">
-        <v>0.45</v>
+        <v>3</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL50" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="AM50" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="AN50" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>96</v>
-      </c>
+        <v>2.85</v>
+      </c>
+      <c r="AO50" t="inlineStr"/>
       <c r="AP50" t="n">
-        <v>72</v>
+        <v>0.65</v>
       </c>
       <c r="AQ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>35</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW50" t="n">
         <v>84</v>
       </c>
     </row>
@@ -7658,25 +8260,26 @@
         <v>3</v>
       </c>
       <c r="M51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N51" t="n">
         <v>3</v>
       </c>
       <c r="O51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P51" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="Q51" t="n">
-        <v>17</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="T51" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -7684,70 +8287,81 @@
       <c r="V51" t="n">
         <v>1</v>
       </c>
-      <c r="W51" t="n">
-        <v>-0.4295698783500092</v>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Z51" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>3</v>
-      </c>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="n">
+        <v>-0.5049679833980029</v>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD51" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>3</v>
       </c>
       <c r="AE51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF51" t="n">
         <v>3</v>
       </c>
       <c r="AG51" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>3</v>
-      </c>
+        <v>3.35</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr"/>
       <c r="AJ51" t="n">
-        <v>0.45</v>
+        <v>2</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL51" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="AM51" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="AN51" t="n">
-        <v>84</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>96</v>
-      </c>
+        <v>2.65</v>
+      </c>
+      <c r="AO51" t="inlineStr"/>
       <c r="AP51" t="n">
-        <v>72</v>
+        <v>0.7</v>
       </c>
       <c r="AQ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>36</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>39</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>88</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>84</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW51" t="n">
         <v>84</v>
       </c>
     </row>
